--- a/public/da3wa-guests-template.xlsx
+++ b/public/da3wa-guests-template.xlsx
@@ -122,10 +122,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -157,10 +157,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -398,12 +398,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D501"/>
+  <dimension ref="A1:E501"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="24.83203125"/>
+    <col min="2" max="2" customWidth="1" width="30.83203125"/>
+    <col min="3" max="3" customWidth="1" width="32.83203125"/>
+    <col min="4" max="4" customWidth="1" width="22.83203125"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,6 +420,9 @@
       <c r="D1" t="str">
         <v>لغة الدعوة (AR أو ENG)</v>
       </c>
+      <c r="E1" t="str">
+        <v>الطرف (العريس أو العروس)</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -433,6 +437,9 @@
       <c r="D2" t="str">
         <v>AR</v>
       </c>
+      <c r="E2" t="str">
+        <v>العريس</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -447,6 +454,9 @@
       <c r="D3" t="str">
         <v>AR</v>
       </c>
+      <c r="E3" t="str">
+        <v>العروس</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -461,6 +471,9 @@
       <c r="D4" t="str">
         <v>ENG</v>
       </c>
+      <c r="E4" t="str">
+        <v>العريس</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="1" t="str">
@@ -2949,7 +2962,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D501"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E501"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/da3wa-guests-template.xlsx
+++ b/public/da3wa-guests-template.xlsx
@@ -64,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -122,10 +121,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -157,10 +156,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -398,13 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E501"/>
+  <dimension ref="A1:F501"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="24.83203125"/>
-    <col min="2" max="2" customWidth="1" width="30.83203125"/>
-    <col min="3" max="3" customWidth="1" width="32.83203125"/>
-    <col min="4" max="4" customWidth="1" width="22.83203125"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
     <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -423,12 +423,15 @@
       <c r="E1" t="str">
         <v>الطرف (العريس أو العروس)</v>
       </c>
+      <c r="F1" t="str">
+        <v>نوع الدعوة (دعوة أو أهل أو مشاركة)</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>أحمد محمد</v>
       </c>
-      <c r="B2" s="1" t="str">
+      <c r="B2" t="str">
         <v>96550012345</v>
       </c>
       <c r="C2">
@@ -439,13 +442,16 @@
       </c>
       <c r="E2" t="str">
         <v>العريس</v>
+      </c>
+      <c r="F2" t="str">
+        <v>دعوة</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>سارة علي</v>
       </c>
-      <c r="B3" s="1" t="str">
+      <c r="B3" t="str">
         <v>966550678901</v>
       </c>
       <c r="C3">
@@ -456,13 +462,16 @@
       </c>
       <c r="E3" t="str">
         <v>العروس</v>
+      </c>
+      <c r="F3" t="str">
+        <v>أهل</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>John Smith</v>
       </c>
-      <c r="B4" s="1" t="str">
+      <c r="B4" t="str">
         <v>447700900123</v>
       </c>
       <c r="C4">
@@ -474,2495 +483,2498 @@
       <c r="E4" t="str">
         <v>العريس</v>
       </c>
+      <c r="F4" t="str">
+        <v>مشاركة</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="1" t="str">
+      <c r="B5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="1" t="str">
+      <c r="B6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="1" t="str">
+      <c r="B7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="1" t="str">
+      <c r="B8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="1" t="str">
+      <c r="B9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="1" t="str">
+      <c r="B10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="1" t="str">
+      <c r="B11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="1" t="str">
+      <c r="B12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="1" t="str">
+      <c r="B13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="1" t="str">
+      <c r="B14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="1" t="str">
+      <c r="B15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="1" t="str">
+      <c r="B16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="1" t="str">
+      <c r="B17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="1" t="str">
+      <c r="B18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="1" t="str">
+      <c r="B19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="1" t="str">
+      <c r="B20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="1" t="str">
+      <c r="B21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="1" t="str">
+      <c r="B22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="1" t="str">
+      <c r="B23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="1" t="str">
+      <c r="B24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="1" t="str">
+      <c r="B25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="1" t="str">
+      <c r="B26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="1" t="str">
+      <c r="B27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="1" t="str">
+      <c r="B28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="1" t="str">
+      <c r="B29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="1" t="str">
+      <c r="B30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="1" t="str">
+      <c r="B31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="1" t="str">
+      <c r="B32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="1" t="str">
+      <c r="B33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="1" t="str">
+      <c r="B34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="1" t="str">
+      <c r="B35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="1" t="str">
+      <c r="B36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="1" t="str">
+      <c r="B37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="1" t="str">
+      <c r="B38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="1" t="str">
+      <c r="B39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="1" t="str">
+      <c r="B40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="1" t="str">
+      <c r="B41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="1" t="str">
+      <c r="B42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="1" t="str">
+      <c r="B43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="1" t="str">
+      <c r="B44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="1" t="str">
+      <c r="B45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="1" t="str">
+      <c r="B46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="1" t="str">
+      <c r="B47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="1" t="str">
+      <c r="B48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="1" t="str">
+      <c r="B49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="1" t="str">
+      <c r="B50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="1" t="str">
+      <c r="B51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="1" t="str">
+      <c r="B52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="1" t="str">
+      <c r="B53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="1" t="str">
+      <c r="B54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="1" t="str">
+      <c r="B55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="1" t="str">
+      <c r="B56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="1" t="str">
+      <c r="B57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="1" t="str">
+      <c r="B58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="1" t="str">
+      <c r="B59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="1" t="str">
+      <c r="B60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="1" t="str">
+      <c r="B61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="1" t="str">
+      <c r="B62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="1" t="str">
+      <c r="B63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="1" t="str">
+      <c r="B64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="1" t="str">
+      <c r="B65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="1" t="str">
+      <c r="B66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="1" t="str">
+      <c r="B67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="1" t="str">
+      <c r="B68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="1" t="str">
+      <c r="B69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="1" t="str">
+      <c r="B70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="1" t="str">
+      <c r="B71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="1" t="str">
+      <c r="B72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="1" t="str">
+      <c r="B73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="1" t="str">
+      <c r="B74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="1" t="str">
+      <c r="B75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="1" t="str">
+      <c r="B76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="1" t="str">
+      <c r="B77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="1" t="str">
+      <c r="B78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="1" t="str">
+      <c r="B79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="1" t="str">
+      <c r="B80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="1" t="str">
+      <c r="B81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="1" t="str">
+      <c r="B82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="1" t="str">
+      <c r="B83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="1" t="str">
+      <c r="B84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="1" t="str">
+      <c r="B85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="1" t="str">
+      <c r="B86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="1" t="str">
+      <c r="B87" t="str">
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="1" t="str">
+      <c r="B88" t="str">
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="1" t="str">
+      <c r="B89" t="str">
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="1" t="str">
+      <c r="B90" t="str">
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="1" t="str">
+      <c r="B91" t="str">
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="1" t="str">
+      <c r="B92" t="str">
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="1" t="str">
+      <c r="B93" t="str">
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="1" t="str">
+      <c r="B94" t="str">
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="1" t="str">
+      <c r="B95" t="str">
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="1" t="str">
+      <c r="B96" t="str">
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="1" t="str">
+      <c r="B97" t="str">
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="1" t="str">
+      <c r="B98" t="str">
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="1" t="str">
+      <c r="B99" t="str">
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="1" t="str">
+      <c r="B100" t="str">
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="1" t="str">
+      <c r="B101" t="str">
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="1" t="str">
+      <c r="B102" t="str">
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="1" t="str">
+      <c r="B103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="1" t="str">
+      <c r="B104" t="str">
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="1" t="str">
+      <c r="B105" t="str">
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="1" t="str">
+      <c r="B106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="1" t="str">
+      <c r="B107" t="str">
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="1" t="str">
+      <c r="B108" t="str">
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="1" t="str">
+      <c r="B109" t="str">
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="1" t="str">
+      <c r="B110" t="str">
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="1" t="str">
+      <c r="B111" t="str">
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="1" t="str">
+      <c r="B112" t="str">
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="1" t="str">
+      <c r="B113" t="str">
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="1" t="str">
+      <c r="B114" t="str">
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="B115" s="1" t="str">
+      <c r="B115" t="str">
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="B116" s="1" t="str">
+      <c r="B116" t="str">
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="1" t="str">
+      <c r="B117" t="str">
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="B118" s="1" t="str">
+      <c r="B118" t="str">
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="1" t="str">
+      <c r="B119" t="str">
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="B120" s="1" t="str">
+      <c r="B120" t="str">
         <v/>
       </c>
     </row>
     <row r="121">
-      <c r="B121" s="1" t="str">
+      <c r="B121" t="str">
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="B122" s="1" t="str">
+      <c r="B122" t="str">
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="B123" s="1" t="str">
+      <c r="B123" t="str">
         <v/>
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="1" t="str">
+      <c r="B124" t="str">
         <v/>
       </c>
     </row>
     <row r="125">
-      <c r="B125" s="1" t="str">
+      <c r="B125" t="str">
         <v/>
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="1" t="str">
+      <c r="B126" t="str">
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="1" t="str">
+      <c r="B127" t="str">
         <v/>
       </c>
     </row>
     <row r="128">
-      <c r="B128" s="1" t="str">
+      <c r="B128" t="str">
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="B129" s="1" t="str">
+      <c r="B129" t="str">
         <v/>
       </c>
     </row>
     <row r="130">
-      <c r="B130" s="1" t="str">
+      <c r="B130" t="str">
         <v/>
       </c>
     </row>
     <row r="131">
-      <c r="B131" s="1" t="str">
+      <c r="B131" t="str">
         <v/>
       </c>
     </row>
     <row r="132">
-      <c r="B132" s="1" t="str">
+      <c r="B132" t="str">
         <v/>
       </c>
     </row>
     <row r="133">
-      <c r="B133" s="1" t="str">
+      <c r="B133" t="str">
         <v/>
       </c>
     </row>
     <row r="134">
-      <c r="B134" s="1" t="str">
+      <c r="B134" t="str">
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="B135" s="1" t="str">
+      <c r="B135" t="str">
         <v/>
       </c>
     </row>
     <row r="136">
-      <c r="B136" s="1" t="str">
+      <c r="B136" t="str">
         <v/>
       </c>
     </row>
     <row r="137">
-      <c r="B137" s="1" t="str">
+      <c r="B137" t="str">
         <v/>
       </c>
     </row>
     <row r="138">
-      <c r="B138" s="1" t="str">
+      <c r="B138" t="str">
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="1" t="str">
+      <c r="B139" t="str">
         <v/>
       </c>
     </row>
     <row r="140">
-      <c r="B140" s="1" t="str">
+      <c r="B140" t="str">
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="B141" s="1" t="str">
+      <c r="B141" t="str">
         <v/>
       </c>
     </row>
     <row r="142">
-      <c r="B142" s="1" t="str">
+      <c r="B142" t="str">
         <v/>
       </c>
     </row>
     <row r="143">
-      <c r="B143" s="1" t="str">
+      <c r="B143" t="str">
         <v/>
       </c>
     </row>
     <row r="144">
-      <c r="B144" s="1" t="str">
+      <c r="B144" t="str">
         <v/>
       </c>
     </row>
     <row r="145">
-      <c r="B145" s="1" t="str">
+      <c r="B145" t="str">
         <v/>
       </c>
     </row>
     <row r="146">
-      <c r="B146" s="1" t="str">
+      <c r="B146" t="str">
         <v/>
       </c>
     </row>
     <row r="147">
-      <c r="B147" s="1" t="str">
+      <c r="B147" t="str">
         <v/>
       </c>
     </row>
     <row r="148">
-      <c r="B148" s="1" t="str">
+      <c r="B148" t="str">
         <v/>
       </c>
     </row>
     <row r="149">
-      <c r="B149" s="1" t="str">
+      <c r="B149" t="str">
         <v/>
       </c>
     </row>
     <row r="150">
-      <c r="B150" s="1" t="str">
+      <c r="B150" t="str">
         <v/>
       </c>
     </row>
     <row r="151">
-      <c r="B151" s="1" t="str">
+      <c r="B151" t="str">
         <v/>
       </c>
     </row>
     <row r="152">
-      <c r="B152" s="1" t="str">
+      <c r="B152" t="str">
         <v/>
       </c>
     </row>
     <row r="153">
-      <c r="B153" s="1" t="str">
+      <c r="B153" t="str">
         <v/>
       </c>
     </row>
     <row r="154">
-      <c r="B154" s="1" t="str">
+      <c r="B154" t="str">
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="B155" s="1" t="str">
+      <c r="B155" t="str">
         <v/>
       </c>
     </row>
     <row r="156">
-      <c r="B156" s="1" t="str">
+      <c r="B156" t="str">
         <v/>
       </c>
     </row>
     <row r="157">
-      <c r="B157" s="1" t="str">
+      <c r="B157" t="str">
         <v/>
       </c>
     </row>
     <row r="158">
-      <c r="B158" s="1" t="str">
+      <c r="B158" t="str">
         <v/>
       </c>
     </row>
     <row r="159">
-      <c r="B159" s="1" t="str">
+      <c r="B159" t="str">
         <v/>
       </c>
     </row>
     <row r="160">
-      <c r="B160" s="1" t="str">
+      <c r="B160" t="str">
         <v/>
       </c>
     </row>
     <row r="161">
-      <c r="B161" s="1" t="str">
+      <c r="B161" t="str">
         <v/>
       </c>
     </row>
     <row r="162">
-      <c r="B162" s="1" t="str">
+      <c r="B162" t="str">
         <v/>
       </c>
     </row>
     <row r="163">
-      <c r="B163" s="1" t="str">
+      <c r="B163" t="str">
         <v/>
       </c>
     </row>
     <row r="164">
-      <c r="B164" s="1" t="str">
+      <c r="B164" t="str">
         <v/>
       </c>
     </row>
     <row r="165">
-      <c r="B165" s="1" t="str">
+      <c r="B165" t="str">
         <v/>
       </c>
     </row>
     <row r="166">
-      <c r="B166" s="1" t="str">
+      <c r="B166" t="str">
         <v/>
       </c>
     </row>
     <row r="167">
-      <c r="B167" s="1" t="str">
+      <c r="B167" t="str">
         <v/>
       </c>
     </row>
     <row r="168">
-      <c r="B168" s="1" t="str">
+      <c r="B168" t="str">
         <v/>
       </c>
     </row>
     <row r="169">
-      <c r="B169" s="1" t="str">
+      <c r="B169" t="str">
         <v/>
       </c>
     </row>
     <row r="170">
-      <c r="B170" s="1" t="str">
+      <c r="B170" t="str">
         <v/>
       </c>
     </row>
     <row r="171">
-      <c r="B171" s="1" t="str">
+      <c r="B171" t="str">
         <v/>
       </c>
     </row>
     <row r="172">
-      <c r="B172" s="1" t="str">
+      <c r="B172" t="str">
         <v/>
       </c>
     </row>
     <row r="173">
-      <c r="B173" s="1" t="str">
+      <c r="B173" t="str">
         <v/>
       </c>
     </row>
     <row r="174">
-      <c r="B174" s="1" t="str">
+      <c r="B174" t="str">
         <v/>
       </c>
     </row>
     <row r="175">
-      <c r="B175" s="1" t="str">
+      <c r="B175" t="str">
         <v/>
       </c>
     </row>
     <row r="176">
-      <c r="B176" s="1" t="str">
+      <c r="B176" t="str">
         <v/>
       </c>
     </row>
     <row r="177">
-      <c r="B177" s="1" t="str">
+      <c r="B177" t="str">
         <v/>
       </c>
     </row>
     <row r="178">
-      <c r="B178" s="1" t="str">
+      <c r="B178" t="str">
         <v/>
       </c>
     </row>
     <row r="179">
-      <c r="B179" s="1" t="str">
+      <c r="B179" t="str">
         <v/>
       </c>
     </row>
     <row r="180">
-      <c r="B180" s="1" t="str">
+      <c r="B180" t="str">
         <v/>
       </c>
     </row>
     <row r="181">
-      <c r="B181" s="1" t="str">
+      <c r="B181" t="str">
         <v/>
       </c>
     </row>
     <row r="182">
-      <c r="B182" s="1" t="str">
+      <c r="B182" t="str">
         <v/>
       </c>
     </row>
     <row r="183">
-      <c r="B183" s="1" t="str">
+      <c r="B183" t="str">
         <v/>
       </c>
     </row>
     <row r="184">
-      <c r="B184" s="1" t="str">
+      <c r="B184" t="str">
         <v/>
       </c>
     </row>
     <row r="185">
-      <c r="B185" s="1" t="str">
+      <c r="B185" t="str">
         <v/>
       </c>
     </row>
     <row r="186">
-      <c r="B186" s="1" t="str">
+      <c r="B186" t="str">
         <v/>
       </c>
     </row>
     <row r="187">
-      <c r="B187" s="1" t="str">
+      <c r="B187" t="str">
         <v/>
       </c>
     </row>
     <row r="188">
-      <c r="B188" s="1" t="str">
+      <c r="B188" t="str">
         <v/>
       </c>
     </row>
     <row r="189">
-      <c r="B189" s="1" t="str">
+      <c r="B189" t="str">
         <v/>
       </c>
     </row>
     <row r="190">
-      <c r="B190" s="1" t="str">
+      <c r="B190" t="str">
         <v/>
       </c>
     </row>
     <row r="191">
-      <c r="B191" s="1" t="str">
+      <c r="B191" t="str">
         <v/>
       </c>
     </row>
     <row r="192">
-      <c r="B192" s="1" t="str">
+      <c r="B192" t="str">
         <v/>
       </c>
     </row>
     <row r="193">
-      <c r="B193" s="1" t="str">
+      <c r="B193" t="str">
         <v/>
       </c>
     </row>
     <row r="194">
-      <c r="B194" s="1" t="str">
+      <c r="B194" t="str">
         <v/>
       </c>
     </row>
     <row r="195">
-      <c r="B195" s="1" t="str">
+      <c r="B195" t="str">
         <v/>
       </c>
     </row>
     <row r="196">
-      <c r="B196" s="1" t="str">
+      <c r="B196" t="str">
         <v/>
       </c>
     </row>
     <row r="197">
-      <c r="B197" s="1" t="str">
+      <c r="B197" t="str">
         <v/>
       </c>
     </row>
     <row r="198">
-      <c r="B198" s="1" t="str">
+      <c r="B198" t="str">
         <v/>
       </c>
     </row>
     <row r="199">
-      <c r="B199" s="1" t="str">
+      <c r="B199" t="str">
         <v/>
       </c>
     </row>
     <row r="200">
-      <c r="B200" s="1" t="str">
+      <c r="B200" t="str">
         <v/>
       </c>
     </row>
     <row r="201">
-      <c r="B201" s="1" t="str">
+      <c r="B201" t="str">
         <v/>
       </c>
     </row>
     <row r="202">
-      <c r="B202" s="1" t="str">
+      <c r="B202" t="str">
         <v/>
       </c>
     </row>
     <row r="203">
-      <c r="B203" s="1" t="str">
+      <c r="B203" t="str">
         <v/>
       </c>
     </row>
     <row r="204">
-      <c r="B204" s="1" t="str">
+      <c r="B204" t="str">
         <v/>
       </c>
     </row>
     <row r="205">
-      <c r="B205" s="1" t="str">
+      <c r="B205" t="str">
         <v/>
       </c>
     </row>
     <row r="206">
-      <c r="B206" s="1" t="str">
+      <c r="B206" t="str">
         <v/>
       </c>
     </row>
     <row r="207">
-      <c r="B207" s="1" t="str">
+      <c r="B207" t="str">
         <v/>
       </c>
     </row>
     <row r="208">
-      <c r="B208" s="1" t="str">
+      <c r="B208" t="str">
         <v/>
       </c>
     </row>
     <row r="209">
-      <c r="B209" s="1" t="str">
+      <c r="B209" t="str">
         <v/>
       </c>
     </row>
     <row r="210">
-      <c r="B210" s="1" t="str">
+      <c r="B210" t="str">
         <v/>
       </c>
     </row>
     <row r="211">
-      <c r="B211" s="1" t="str">
+      <c r="B211" t="str">
         <v/>
       </c>
     </row>
     <row r="212">
-      <c r="B212" s="1" t="str">
+      <c r="B212" t="str">
         <v/>
       </c>
     </row>
     <row r="213">
-      <c r="B213" s="1" t="str">
+      <c r="B213" t="str">
         <v/>
       </c>
     </row>
     <row r="214">
-      <c r="B214" s="1" t="str">
+      <c r="B214" t="str">
         <v/>
       </c>
     </row>
     <row r="215">
-      <c r="B215" s="1" t="str">
+      <c r="B215" t="str">
         <v/>
       </c>
     </row>
     <row r="216">
-      <c r="B216" s="1" t="str">
+      <c r="B216" t="str">
         <v/>
       </c>
     </row>
     <row r="217">
-      <c r="B217" s="1" t="str">
+      <c r="B217" t="str">
         <v/>
       </c>
     </row>
     <row r="218">
-      <c r="B218" s="1" t="str">
+      <c r="B218" t="str">
         <v/>
       </c>
     </row>
     <row r="219">
-      <c r="B219" s="1" t="str">
+      <c r="B219" t="str">
         <v/>
       </c>
     </row>
     <row r="220">
-      <c r="B220" s="1" t="str">
+      <c r="B220" t="str">
         <v/>
       </c>
     </row>
     <row r="221">
-      <c r="B221" s="1" t="str">
+      <c r="B221" t="str">
         <v/>
       </c>
     </row>
     <row r="222">
-      <c r="B222" s="1" t="str">
+      <c r="B222" t="str">
         <v/>
       </c>
     </row>
     <row r="223">
-      <c r="B223" s="1" t="str">
+      <c r="B223" t="str">
         <v/>
       </c>
     </row>
     <row r="224">
-      <c r="B224" s="1" t="str">
+      <c r="B224" t="str">
         <v/>
       </c>
     </row>
     <row r="225">
-      <c r="B225" s="1" t="str">
+      <c r="B225" t="str">
         <v/>
       </c>
     </row>
     <row r="226">
-      <c r="B226" s="1" t="str">
+      <c r="B226" t="str">
         <v/>
       </c>
     </row>
     <row r="227">
-      <c r="B227" s="1" t="str">
+      <c r="B227" t="str">
         <v/>
       </c>
     </row>
     <row r="228">
-      <c r="B228" s="1" t="str">
+      <c r="B228" t="str">
         <v/>
       </c>
     </row>
     <row r="229">
-      <c r="B229" s="1" t="str">
+      <c r="B229" t="str">
         <v/>
       </c>
     </row>
     <row r="230">
-      <c r="B230" s="1" t="str">
+      <c r="B230" t="str">
         <v/>
       </c>
     </row>
     <row r="231">
-      <c r="B231" s="1" t="str">
+      <c r="B231" t="str">
         <v/>
       </c>
     </row>
     <row r="232">
-      <c r="B232" s="1" t="str">
+      <c r="B232" t="str">
         <v/>
       </c>
     </row>
     <row r="233">
-      <c r="B233" s="1" t="str">
+      <c r="B233" t="str">
         <v/>
       </c>
     </row>
     <row r="234">
-      <c r="B234" s="1" t="str">
+      <c r="B234" t="str">
         <v/>
       </c>
     </row>
     <row r="235">
-      <c r="B235" s="1" t="str">
+      <c r="B235" t="str">
         <v/>
       </c>
     </row>
     <row r="236">
-      <c r="B236" s="1" t="str">
+      <c r="B236" t="str">
         <v/>
       </c>
     </row>
     <row r="237">
-      <c r="B237" s="1" t="str">
+      <c r="B237" t="str">
         <v/>
       </c>
     </row>
     <row r="238">
-      <c r="B238" s="1" t="str">
+      <c r="B238" t="str">
         <v/>
       </c>
     </row>
     <row r="239">
-      <c r="B239" s="1" t="str">
+      <c r="B239" t="str">
         <v/>
       </c>
     </row>
     <row r="240">
-      <c r="B240" s="1" t="str">
+      <c r="B240" t="str">
         <v/>
       </c>
     </row>
     <row r="241">
-      <c r="B241" s="1" t="str">
+      <c r="B241" t="str">
         <v/>
       </c>
     </row>
     <row r="242">
-      <c r="B242" s="1" t="str">
+      <c r="B242" t="str">
         <v/>
       </c>
     </row>
     <row r="243">
-      <c r="B243" s="1" t="str">
+      <c r="B243" t="str">
         <v/>
       </c>
     </row>
     <row r="244">
-      <c r="B244" s="1" t="str">
+      <c r="B244" t="str">
         <v/>
       </c>
     </row>
     <row r="245">
-      <c r="B245" s="1" t="str">
+      <c r="B245" t="str">
         <v/>
       </c>
     </row>
     <row r="246">
-      <c r="B246" s="1" t="str">
+      <c r="B246" t="str">
         <v/>
       </c>
     </row>
     <row r="247">
-      <c r="B247" s="1" t="str">
+      <c r="B247" t="str">
         <v/>
       </c>
     </row>
     <row r="248">
-      <c r="B248" s="1" t="str">
+      <c r="B248" t="str">
         <v/>
       </c>
     </row>
     <row r="249">
-      <c r="B249" s="1" t="str">
+      <c r="B249" t="str">
         <v/>
       </c>
     </row>
     <row r="250">
-      <c r="B250" s="1" t="str">
+      <c r="B250" t="str">
         <v/>
       </c>
     </row>
     <row r="251">
-      <c r="B251" s="1" t="str">
+      <c r="B251" t="str">
         <v/>
       </c>
     </row>
     <row r="252">
-      <c r="B252" s="1" t="str">
+      <c r="B252" t="str">
         <v/>
       </c>
     </row>
     <row r="253">
-      <c r="B253" s="1" t="str">
+      <c r="B253" t="str">
         <v/>
       </c>
     </row>
     <row r="254">
-      <c r="B254" s="1" t="str">
+      <c r="B254" t="str">
         <v/>
       </c>
     </row>
     <row r="255">
-      <c r="B255" s="1" t="str">
+      <c r="B255" t="str">
         <v/>
       </c>
     </row>
     <row r="256">
-      <c r="B256" s="1" t="str">
+      <c r="B256" t="str">
         <v/>
       </c>
     </row>
     <row r="257">
-      <c r="B257" s="1" t="str">
+      <c r="B257" t="str">
         <v/>
       </c>
     </row>
     <row r="258">
-      <c r="B258" s="1" t="str">
+      <c r="B258" t="str">
         <v/>
       </c>
     </row>
     <row r="259">
-      <c r="B259" s="1" t="str">
+      <c r="B259" t="str">
         <v/>
       </c>
     </row>
     <row r="260">
-      <c r="B260" s="1" t="str">
+      <c r="B260" t="str">
         <v/>
       </c>
     </row>
     <row r="261">
-      <c r="B261" s="1" t="str">
+      <c r="B261" t="str">
         <v/>
       </c>
     </row>
     <row r="262">
-      <c r="B262" s="1" t="str">
+      <c r="B262" t="str">
         <v/>
       </c>
     </row>
     <row r="263">
-      <c r="B263" s="1" t="str">
+      <c r="B263" t="str">
         <v/>
       </c>
     </row>
     <row r="264">
-      <c r="B264" s="1" t="str">
+      <c r="B264" t="str">
         <v/>
       </c>
     </row>
     <row r="265">
-      <c r="B265" s="1" t="str">
+      <c r="B265" t="str">
         <v/>
       </c>
     </row>
     <row r="266">
-      <c r="B266" s="1" t="str">
+      <c r="B266" t="str">
         <v/>
       </c>
     </row>
     <row r="267">
-      <c r="B267" s="1" t="str">
+      <c r="B267" t="str">
         <v/>
       </c>
     </row>
     <row r="268">
-      <c r="B268" s="1" t="str">
+      <c r="B268" t="str">
         <v/>
       </c>
     </row>
     <row r="269">
-      <c r="B269" s="1" t="str">
+      <c r="B269" t="str">
         <v/>
       </c>
     </row>
     <row r="270">
-      <c r="B270" s="1" t="str">
+      <c r="B270" t="str">
         <v/>
       </c>
     </row>
     <row r="271">
-      <c r="B271" s="1" t="str">
+      <c r="B271" t="str">
         <v/>
       </c>
     </row>
     <row r="272">
-      <c r="B272" s="1" t="str">
+      <c r="B272" t="str">
         <v/>
       </c>
     </row>
     <row r="273">
-      <c r="B273" s="1" t="str">
+      <c r="B273" t="str">
         <v/>
       </c>
     </row>
     <row r="274">
-      <c r="B274" s="1" t="str">
+      <c r="B274" t="str">
         <v/>
       </c>
     </row>
     <row r="275">
-      <c r="B275" s="1" t="str">
+      <c r="B275" t="str">
         <v/>
       </c>
     </row>
     <row r="276">
-      <c r="B276" s="1" t="str">
+      <c r="B276" t="str">
         <v/>
       </c>
     </row>
     <row r="277">
-      <c r="B277" s="1" t="str">
+      <c r="B277" t="str">
         <v/>
       </c>
     </row>
     <row r="278">
-      <c r="B278" s="1" t="str">
+      <c r="B278" t="str">
         <v/>
       </c>
     </row>
     <row r="279">
-      <c r="B279" s="1" t="str">
+      <c r="B279" t="str">
         <v/>
       </c>
     </row>
     <row r="280">
-      <c r="B280" s="1" t="str">
+      <c r="B280" t="str">
         <v/>
       </c>
     </row>
     <row r="281">
-      <c r="B281" s="1" t="str">
+      <c r="B281" t="str">
         <v/>
       </c>
     </row>
     <row r="282">
-      <c r="B282" s="1" t="str">
+      <c r="B282" t="str">
         <v/>
       </c>
     </row>
     <row r="283">
-      <c r="B283" s="1" t="str">
+      <c r="B283" t="str">
         <v/>
       </c>
     </row>
     <row r="284">
-      <c r="B284" s="1" t="str">
+      <c r="B284" t="str">
         <v/>
       </c>
     </row>
     <row r="285">
-      <c r="B285" s="1" t="str">
+      <c r="B285" t="str">
         <v/>
       </c>
     </row>
     <row r="286">
-      <c r="B286" s="1" t="str">
+      <c r="B286" t="str">
         <v/>
       </c>
     </row>
     <row r="287">
-      <c r="B287" s="1" t="str">
+      <c r="B287" t="str">
         <v/>
       </c>
     </row>
     <row r="288">
-      <c r="B288" s="1" t="str">
+      <c r="B288" t="str">
         <v/>
       </c>
     </row>
     <row r="289">
-      <c r="B289" s="1" t="str">
+      <c r="B289" t="str">
         <v/>
       </c>
     </row>
     <row r="290">
-      <c r="B290" s="1" t="str">
+      <c r="B290" t="str">
         <v/>
       </c>
     </row>
     <row r="291">
-      <c r="B291" s="1" t="str">
+      <c r="B291" t="str">
         <v/>
       </c>
     </row>
     <row r="292">
-      <c r="B292" s="1" t="str">
+      <c r="B292" t="str">
         <v/>
       </c>
     </row>
     <row r="293">
-      <c r="B293" s="1" t="str">
+      <c r="B293" t="str">
         <v/>
       </c>
     </row>
     <row r="294">
-      <c r="B294" s="1" t="str">
+      <c r="B294" t="str">
         <v/>
       </c>
     </row>
     <row r="295">
-      <c r="B295" s="1" t="str">
+      <c r="B295" t="str">
         <v/>
       </c>
     </row>
     <row r="296">
-      <c r="B296" s="1" t="str">
+      <c r="B296" t="str">
         <v/>
       </c>
     </row>
     <row r="297">
-      <c r="B297" s="1" t="str">
+      <c r="B297" t="str">
         <v/>
       </c>
     </row>
     <row r="298">
-      <c r="B298" s="1" t="str">
+      <c r="B298" t="str">
         <v/>
       </c>
     </row>
     <row r="299">
-      <c r="B299" s="1" t="str">
+      <c r="B299" t="str">
         <v/>
       </c>
     </row>
     <row r="300">
-      <c r="B300" s="1" t="str">
+      <c r="B300" t="str">
         <v/>
       </c>
     </row>
     <row r="301">
-      <c r="B301" s="1" t="str">
+      <c r="B301" t="str">
         <v/>
       </c>
     </row>
     <row r="302">
-      <c r="B302" s="1" t="str">
+      <c r="B302" t="str">
         <v/>
       </c>
     </row>
     <row r="303">
-      <c r="B303" s="1" t="str">
+      <c r="B303" t="str">
         <v/>
       </c>
     </row>
     <row r="304">
-      <c r="B304" s="1" t="str">
+      <c r="B304" t="str">
         <v/>
       </c>
     </row>
     <row r="305">
-      <c r="B305" s="1" t="str">
+      <c r="B305" t="str">
         <v/>
       </c>
     </row>
     <row r="306">
-      <c r="B306" s="1" t="str">
+      <c r="B306" t="str">
         <v/>
       </c>
     </row>
     <row r="307">
-      <c r="B307" s="1" t="str">
+      <c r="B307" t="str">
         <v/>
       </c>
     </row>
     <row r="308">
-      <c r="B308" s="1" t="str">
+      <c r="B308" t="str">
         <v/>
       </c>
     </row>
     <row r="309">
-      <c r="B309" s="1" t="str">
+      <c r="B309" t="str">
         <v/>
       </c>
     </row>
     <row r="310">
-      <c r="B310" s="1" t="str">
+      <c r="B310" t="str">
         <v/>
       </c>
     </row>
     <row r="311">
-      <c r="B311" s="1" t="str">
+      <c r="B311" t="str">
         <v/>
       </c>
     </row>
     <row r="312">
-      <c r="B312" s="1" t="str">
+      <c r="B312" t="str">
         <v/>
       </c>
     </row>
     <row r="313">
-      <c r="B313" s="1" t="str">
+      <c r="B313" t="str">
         <v/>
       </c>
     </row>
     <row r="314">
-      <c r="B314" s="1" t="str">
+      <c r="B314" t="str">
         <v/>
       </c>
     </row>
     <row r="315">
-      <c r="B315" s="1" t="str">
+      <c r="B315" t="str">
         <v/>
       </c>
     </row>
     <row r="316">
-      <c r="B316" s="1" t="str">
+      <c r="B316" t="str">
         <v/>
       </c>
     </row>
     <row r="317">
-      <c r="B317" s="1" t="str">
+      <c r="B317" t="str">
         <v/>
       </c>
     </row>
     <row r="318">
-      <c r="B318" s="1" t="str">
+      <c r="B318" t="str">
         <v/>
       </c>
     </row>
     <row r="319">
-      <c r="B319" s="1" t="str">
+      <c r="B319" t="str">
         <v/>
       </c>
     </row>
     <row r="320">
-      <c r="B320" s="1" t="str">
+      <c r="B320" t="str">
         <v/>
       </c>
     </row>
     <row r="321">
-      <c r="B321" s="1" t="str">
+      <c r="B321" t="str">
         <v/>
       </c>
     </row>
     <row r="322">
-      <c r="B322" s="1" t="str">
+      <c r="B322" t="str">
         <v/>
       </c>
     </row>
     <row r="323">
-      <c r="B323" s="1" t="str">
+      <c r="B323" t="str">
         <v/>
       </c>
     </row>
     <row r="324">
-      <c r="B324" s="1" t="str">
+      <c r="B324" t="str">
         <v/>
       </c>
     </row>
     <row r="325">
-      <c r="B325" s="1" t="str">
+      <c r="B325" t="str">
         <v/>
       </c>
     </row>
     <row r="326">
-      <c r="B326" s="1" t="str">
+      <c r="B326" t="str">
         <v/>
       </c>
     </row>
     <row r="327">
-      <c r="B327" s="1" t="str">
+      <c r="B327" t="str">
         <v/>
       </c>
     </row>
     <row r="328">
-      <c r="B328" s="1" t="str">
+      <c r="B328" t="str">
         <v/>
       </c>
     </row>
     <row r="329">
-      <c r="B329" s="1" t="str">
+      <c r="B329" t="str">
         <v/>
       </c>
     </row>
     <row r="330">
-      <c r="B330" s="1" t="str">
+      <c r="B330" t="str">
         <v/>
       </c>
     </row>
     <row r="331">
-      <c r="B331" s="1" t="str">
+      <c r="B331" t="str">
         <v/>
       </c>
     </row>
     <row r="332">
-      <c r="B332" s="1" t="str">
+      <c r="B332" t="str">
         <v/>
       </c>
     </row>
     <row r="333">
-      <c r="B333" s="1" t="str">
+      <c r="B333" t="str">
         <v/>
       </c>
     </row>
     <row r="334">
-      <c r="B334" s="1" t="str">
+      <c r="B334" t="str">
         <v/>
       </c>
     </row>
     <row r="335">
-      <c r="B335" s="1" t="str">
+      <c r="B335" t="str">
         <v/>
       </c>
     </row>
     <row r="336">
-      <c r="B336" s="1" t="str">
+      <c r="B336" t="str">
         <v/>
       </c>
     </row>
     <row r="337">
-      <c r="B337" s="1" t="str">
+      <c r="B337" t="str">
         <v/>
       </c>
     </row>
     <row r="338">
-      <c r="B338" s="1" t="str">
+      <c r="B338" t="str">
         <v/>
       </c>
     </row>
     <row r="339">
-      <c r="B339" s="1" t="str">
+      <c r="B339" t="str">
         <v/>
       </c>
     </row>
     <row r="340">
-      <c r="B340" s="1" t="str">
+      <c r="B340" t="str">
         <v/>
       </c>
     </row>
     <row r="341">
-      <c r="B341" s="1" t="str">
+      <c r="B341" t="str">
         <v/>
       </c>
     </row>
     <row r="342">
-      <c r="B342" s="1" t="str">
+      <c r="B342" t="str">
         <v/>
       </c>
     </row>
     <row r="343">
-      <c r="B343" s="1" t="str">
+      <c r="B343" t="str">
         <v/>
       </c>
     </row>
     <row r="344">
-      <c r="B344" s="1" t="str">
+      <c r="B344" t="str">
         <v/>
       </c>
     </row>
     <row r="345">
-      <c r="B345" s="1" t="str">
+      <c r="B345" t="str">
         <v/>
       </c>
     </row>
     <row r="346">
-      <c r="B346" s="1" t="str">
+      <c r="B346" t="str">
         <v/>
       </c>
     </row>
     <row r="347">
-      <c r="B347" s="1" t="str">
+      <c r="B347" t="str">
         <v/>
       </c>
     </row>
     <row r="348">
-      <c r="B348" s="1" t="str">
+      <c r="B348" t="str">
         <v/>
       </c>
     </row>
     <row r="349">
-      <c r="B349" s="1" t="str">
+      <c r="B349" t="str">
         <v/>
       </c>
     </row>
     <row r="350">
-      <c r="B350" s="1" t="str">
+      <c r="B350" t="str">
         <v/>
       </c>
     </row>
     <row r="351">
-      <c r="B351" s="1" t="str">
+      <c r="B351" t="str">
         <v/>
       </c>
     </row>
     <row r="352">
-      <c r="B352" s="1" t="str">
+      <c r="B352" t="str">
         <v/>
       </c>
     </row>
     <row r="353">
-      <c r="B353" s="1" t="str">
+      <c r="B353" t="str">
         <v/>
       </c>
     </row>
     <row r="354">
-      <c r="B354" s="1" t="str">
+      <c r="B354" t="str">
         <v/>
       </c>
     </row>
     <row r="355">
-      <c r="B355" s="1" t="str">
+      <c r="B355" t="str">
         <v/>
       </c>
     </row>
     <row r="356">
-      <c r="B356" s="1" t="str">
+      <c r="B356" t="str">
         <v/>
       </c>
     </row>
     <row r="357">
-      <c r="B357" s="1" t="str">
+      <c r="B357" t="str">
         <v/>
       </c>
     </row>
     <row r="358">
-      <c r="B358" s="1" t="str">
+      <c r="B358" t="str">
         <v/>
       </c>
     </row>
     <row r="359">
-      <c r="B359" s="1" t="str">
+      <c r="B359" t="str">
         <v/>
       </c>
     </row>
     <row r="360">
-      <c r="B360" s="1" t="str">
+      <c r="B360" t="str">
         <v/>
       </c>
     </row>
     <row r="361">
-      <c r="B361" s="1" t="str">
+      <c r="B361" t="str">
         <v/>
       </c>
     </row>
     <row r="362">
-      <c r="B362" s="1" t="str">
+      <c r="B362" t="str">
         <v/>
       </c>
     </row>
     <row r="363">
-      <c r="B363" s="1" t="str">
+      <c r="B363" t="str">
         <v/>
       </c>
     </row>
     <row r="364">
-      <c r="B364" s="1" t="str">
+      <c r="B364" t="str">
         <v/>
       </c>
     </row>
     <row r="365">
-      <c r="B365" s="1" t="str">
+      <c r="B365" t="str">
         <v/>
       </c>
     </row>
     <row r="366">
-      <c r="B366" s="1" t="str">
+      <c r="B366" t="str">
         <v/>
       </c>
     </row>
     <row r="367">
-      <c r="B367" s="1" t="str">
+      <c r="B367" t="str">
         <v/>
       </c>
     </row>
     <row r="368">
-      <c r="B368" s="1" t="str">
+      <c r="B368" t="str">
         <v/>
       </c>
     </row>
     <row r="369">
-      <c r="B369" s="1" t="str">
+      <c r="B369" t="str">
         <v/>
       </c>
     </row>
     <row r="370">
-      <c r="B370" s="1" t="str">
+      <c r="B370" t="str">
         <v/>
       </c>
     </row>
     <row r="371">
-      <c r="B371" s="1" t="str">
+      <c r="B371" t="str">
         <v/>
       </c>
     </row>
     <row r="372">
-      <c r="B372" s="1" t="str">
+      <c r="B372" t="str">
         <v/>
       </c>
     </row>
     <row r="373">
-      <c r="B373" s="1" t="str">
+      <c r="B373" t="str">
         <v/>
       </c>
     </row>
     <row r="374">
-      <c r="B374" s="1" t="str">
+      <c r="B374" t="str">
         <v/>
       </c>
     </row>
     <row r="375">
-      <c r="B375" s="1" t="str">
+      <c r="B375" t="str">
         <v/>
       </c>
     </row>
     <row r="376">
-      <c r="B376" s="1" t="str">
+      <c r="B376" t="str">
         <v/>
       </c>
     </row>
     <row r="377">
-      <c r="B377" s="1" t="str">
+      <c r="B377" t="str">
         <v/>
       </c>
     </row>
     <row r="378">
-      <c r="B378" s="1" t="str">
+      <c r="B378" t="str">
         <v/>
       </c>
     </row>
     <row r="379">
-      <c r="B379" s="1" t="str">
+      <c r="B379" t="str">
         <v/>
       </c>
     </row>
     <row r="380">
-      <c r="B380" s="1" t="str">
+      <c r="B380" t="str">
         <v/>
       </c>
     </row>
     <row r="381">
-      <c r="B381" s="1" t="str">
+      <c r="B381" t="str">
         <v/>
       </c>
     </row>
     <row r="382">
-      <c r="B382" s="1" t="str">
+      <c r="B382" t="str">
         <v/>
       </c>
     </row>
     <row r="383">
-      <c r="B383" s="1" t="str">
+      <c r="B383" t="str">
         <v/>
       </c>
     </row>
     <row r="384">
-      <c r="B384" s="1" t="str">
+      <c r="B384" t="str">
         <v/>
       </c>
     </row>
     <row r="385">
-      <c r="B385" s="1" t="str">
+      <c r="B385" t="str">
         <v/>
       </c>
     </row>
     <row r="386">
-      <c r="B386" s="1" t="str">
+      <c r="B386" t="str">
         <v/>
       </c>
     </row>
     <row r="387">
-      <c r="B387" s="1" t="str">
+      <c r="B387" t="str">
         <v/>
       </c>
     </row>
     <row r="388">
-      <c r="B388" s="1" t="str">
+      <c r="B388" t="str">
         <v/>
       </c>
     </row>
     <row r="389">
-      <c r="B389" s="1" t="str">
+      <c r="B389" t="str">
         <v/>
       </c>
     </row>
     <row r="390">
-      <c r="B390" s="1" t="str">
+      <c r="B390" t="str">
         <v/>
       </c>
     </row>
     <row r="391">
-      <c r="B391" s="1" t="str">
+      <c r="B391" t="str">
         <v/>
       </c>
     </row>
     <row r="392">
-      <c r="B392" s="1" t="str">
+      <c r="B392" t="str">
         <v/>
       </c>
     </row>
     <row r="393">
-      <c r="B393" s="1" t="str">
+      <c r="B393" t="str">
         <v/>
       </c>
     </row>
     <row r="394">
-      <c r="B394" s="1" t="str">
+      <c r="B394" t="str">
         <v/>
       </c>
     </row>
     <row r="395">
-      <c r="B395" s="1" t="str">
+      <c r="B395" t="str">
         <v/>
       </c>
     </row>
     <row r="396">
-      <c r="B396" s="1" t="str">
+      <c r="B396" t="str">
         <v/>
       </c>
     </row>
     <row r="397">
-      <c r="B397" s="1" t="str">
+      <c r="B397" t="str">
         <v/>
       </c>
     </row>
     <row r="398">
-      <c r="B398" s="1" t="str">
+      <c r="B398" t="str">
         <v/>
       </c>
     </row>
     <row r="399">
-      <c r="B399" s="1" t="str">
+      <c r="B399" t="str">
         <v/>
       </c>
     </row>
     <row r="400">
-      <c r="B400" s="1" t="str">
+      <c r="B400" t="str">
         <v/>
       </c>
     </row>
     <row r="401">
-      <c r="B401" s="1" t="str">
+      <c r="B401" t="str">
         <v/>
       </c>
     </row>
     <row r="402">
-      <c r="B402" s="1" t="str">
+      <c r="B402" t="str">
         <v/>
       </c>
     </row>
     <row r="403">
-      <c r="B403" s="1" t="str">
+      <c r="B403" t="str">
         <v/>
       </c>
     </row>
     <row r="404">
-      <c r="B404" s="1" t="str">
+      <c r="B404" t="str">
         <v/>
       </c>
     </row>
     <row r="405">
-      <c r="B405" s="1" t="str">
+      <c r="B405" t="str">
         <v/>
       </c>
     </row>
     <row r="406">
-      <c r="B406" s="1" t="str">
+      <c r="B406" t="str">
         <v/>
       </c>
     </row>
     <row r="407">
-      <c r="B407" s="1" t="str">
+      <c r="B407" t="str">
         <v/>
       </c>
     </row>
     <row r="408">
-      <c r="B408" s="1" t="str">
+      <c r="B408" t="str">
         <v/>
       </c>
     </row>
     <row r="409">
-      <c r="B409" s="1" t="str">
+      <c r="B409" t="str">
         <v/>
       </c>
     </row>
     <row r="410">
-      <c r="B410" s="1" t="str">
+      <c r="B410" t="str">
         <v/>
       </c>
     </row>
     <row r="411">
-      <c r="B411" s="1" t="str">
+      <c r="B411" t="str">
         <v/>
       </c>
     </row>
     <row r="412">
-      <c r="B412" s="1" t="str">
+      <c r="B412" t="str">
         <v/>
       </c>
     </row>
     <row r="413">
-      <c r="B413" s="1" t="str">
+      <c r="B413" t="str">
         <v/>
       </c>
     </row>
     <row r="414">
-      <c r="B414" s="1" t="str">
+      <c r="B414" t="str">
         <v/>
       </c>
     </row>
     <row r="415">
-      <c r="B415" s="1" t="str">
+      <c r="B415" t="str">
         <v/>
       </c>
     </row>
     <row r="416">
-      <c r="B416" s="1" t="str">
+      <c r="B416" t="str">
         <v/>
       </c>
     </row>
     <row r="417">
-      <c r="B417" s="1" t="str">
+      <c r="B417" t="str">
         <v/>
       </c>
     </row>
     <row r="418">
-      <c r="B418" s="1" t="str">
+      <c r="B418" t="str">
         <v/>
       </c>
     </row>
     <row r="419">
-      <c r="B419" s="1" t="str">
+      <c r="B419" t="str">
         <v/>
       </c>
     </row>
     <row r="420">
-      <c r="B420" s="1" t="str">
+      <c r="B420" t="str">
         <v/>
       </c>
     </row>
     <row r="421">
-      <c r="B421" s="1" t="str">
+      <c r="B421" t="str">
         <v/>
       </c>
     </row>
     <row r="422">
-      <c r="B422" s="1" t="str">
+      <c r="B422" t="str">
         <v/>
       </c>
     </row>
     <row r="423">
-      <c r="B423" s="1" t="str">
+      <c r="B423" t="str">
         <v/>
       </c>
     </row>
     <row r="424">
-      <c r="B424" s="1" t="str">
+      <c r="B424" t="str">
         <v/>
       </c>
     </row>
     <row r="425">
-      <c r="B425" s="1" t="str">
+      <c r="B425" t="str">
         <v/>
       </c>
     </row>
     <row r="426">
-      <c r="B426" s="1" t="str">
+      <c r="B426" t="str">
         <v/>
       </c>
     </row>
     <row r="427">
-      <c r="B427" s="1" t="str">
+      <c r="B427" t="str">
         <v/>
       </c>
     </row>
     <row r="428">
-      <c r="B428" s="1" t="str">
+      <c r="B428" t="str">
         <v/>
       </c>
     </row>
     <row r="429">
-      <c r="B429" s="1" t="str">
+      <c r="B429" t="str">
         <v/>
       </c>
     </row>
     <row r="430">
-      <c r="B430" s="1" t="str">
+      <c r="B430" t="str">
         <v/>
       </c>
     </row>
     <row r="431">
-      <c r="B431" s="1" t="str">
+      <c r="B431" t="str">
         <v/>
       </c>
     </row>
     <row r="432">
-      <c r="B432" s="1" t="str">
+      <c r="B432" t="str">
         <v/>
       </c>
     </row>
     <row r="433">
-      <c r="B433" s="1" t="str">
+      <c r="B433" t="str">
         <v/>
       </c>
     </row>
     <row r="434">
-      <c r="B434" s="1" t="str">
+      <c r="B434" t="str">
         <v/>
       </c>
     </row>
     <row r="435">
-      <c r="B435" s="1" t="str">
+      <c r="B435" t="str">
         <v/>
       </c>
     </row>
     <row r="436">
-      <c r="B436" s="1" t="str">
+      <c r="B436" t="str">
         <v/>
       </c>
     </row>
     <row r="437">
-      <c r="B437" s="1" t="str">
+      <c r="B437" t="str">
         <v/>
       </c>
     </row>
     <row r="438">
-      <c r="B438" s="1" t="str">
+      <c r="B438" t="str">
         <v/>
       </c>
     </row>
     <row r="439">
-      <c r="B439" s="1" t="str">
+      <c r="B439" t="str">
         <v/>
       </c>
     </row>
     <row r="440">
-      <c r="B440" s="1" t="str">
+      <c r="B440" t="str">
         <v/>
       </c>
     </row>
     <row r="441">
-      <c r="B441" s="1" t="str">
+      <c r="B441" t="str">
         <v/>
       </c>
     </row>
     <row r="442">
-      <c r="B442" s="1" t="str">
+      <c r="B442" t="str">
         <v/>
       </c>
     </row>
     <row r="443">
-      <c r="B443" s="1" t="str">
+      <c r="B443" t="str">
         <v/>
       </c>
     </row>
     <row r="444">
-      <c r="B444" s="1" t="str">
+      <c r="B444" t="str">
         <v/>
       </c>
     </row>
     <row r="445">
-      <c r="B445" s="1" t="str">
+      <c r="B445" t="str">
         <v/>
       </c>
     </row>
     <row r="446">
-      <c r="B446" s="1" t="str">
+      <c r="B446" t="str">
         <v/>
       </c>
     </row>
     <row r="447">
-      <c r="B447" s="1" t="str">
+      <c r="B447" t="str">
         <v/>
       </c>
     </row>
     <row r="448">
-      <c r="B448" s="1" t="str">
+      <c r="B448" t="str">
         <v/>
       </c>
     </row>
     <row r="449">
-      <c r="B449" s="1" t="str">
+      <c r="B449" t="str">
         <v/>
       </c>
     </row>
     <row r="450">
-      <c r="B450" s="1" t="str">
+      <c r="B450" t="str">
         <v/>
       </c>
     </row>
     <row r="451">
-      <c r="B451" s="1" t="str">
+      <c r="B451" t="str">
         <v/>
       </c>
     </row>
     <row r="452">
-      <c r="B452" s="1" t="str">
+      <c r="B452" t="str">
         <v/>
       </c>
     </row>
     <row r="453">
-      <c r="B453" s="1" t="str">
+      <c r="B453" t="str">
         <v/>
       </c>
     </row>
     <row r="454">
-      <c r="B454" s="1" t="str">
+      <c r="B454" t="str">
         <v/>
       </c>
     </row>
     <row r="455">
-      <c r="B455" s="1" t="str">
+      <c r="B455" t="str">
         <v/>
       </c>
     </row>
     <row r="456">
-      <c r="B456" s="1" t="str">
+      <c r="B456" t="str">
         <v/>
       </c>
     </row>
     <row r="457">
-      <c r="B457" s="1" t="str">
+      <c r="B457" t="str">
         <v/>
       </c>
     </row>
     <row r="458">
-      <c r="B458" s="1" t="str">
+      <c r="B458" t="str">
         <v/>
       </c>
     </row>
     <row r="459">
-      <c r="B459" s="1" t="str">
+      <c r="B459" t="str">
         <v/>
       </c>
     </row>
     <row r="460">
-      <c r="B460" s="1" t="str">
+      <c r="B460" t="str">
         <v/>
       </c>
     </row>
     <row r="461">
-      <c r="B461" s="1" t="str">
+      <c r="B461" t="str">
         <v/>
       </c>
     </row>
     <row r="462">
-      <c r="B462" s="1" t="str">
+      <c r="B462" t="str">
         <v/>
       </c>
     </row>
     <row r="463">
-      <c r="B463" s="1" t="str">
+      <c r="B463" t="str">
         <v/>
       </c>
     </row>
     <row r="464">
-      <c r="B464" s="1" t="str">
+      <c r="B464" t="str">
         <v/>
       </c>
     </row>
     <row r="465">
-      <c r="B465" s="1" t="str">
+      <c r="B465" t="str">
         <v/>
       </c>
     </row>
     <row r="466">
-      <c r="B466" s="1" t="str">
+      <c r="B466" t="str">
         <v/>
       </c>
     </row>
     <row r="467">
-      <c r="B467" s="1" t="str">
+      <c r="B467" t="str">
         <v/>
       </c>
     </row>
     <row r="468">
-      <c r="B468" s="1" t="str">
+      <c r="B468" t="str">
         <v/>
       </c>
     </row>
     <row r="469">
-      <c r="B469" s="1" t="str">
+      <c r="B469" t="str">
         <v/>
       </c>
     </row>
     <row r="470">
-      <c r="B470" s="1" t="str">
+      <c r="B470" t="str">
         <v/>
       </c>
     </row>
     <row r="471">
-      <c r="B471" s="1" t="str">
+      <c r="B471" t="str">
         <v/>
       </c>
     </row>
     <row r="472">
-      <c r="B472" s="1" t="str">
+      <c r="B472" t="str">
         <v/>
       </c>
     </row>
     <row r="473">
-      <c r="B473" s="1" t="str">
+      <c r="B473" t="str">
         <v/>
       </c>
     </row>
     <row r="474">
-      <c r="B474" s="1" t="str">
+      <c r="B474" t="str">
         <v/>
       </c>
     </row>
     <row r="475">
-      <c r="B475" s="1" t="str">
+      <c r="B475" t="str">
         <v/>
       </c>
     </row>
     <row r="476">
-      <c r="B476" s="1" t="str">
+      <c r="B476" t="str">
         <v/>
       </c>
     </row>
     <row r="477">
-      <c r="B477" s="1" t="str">
+      <c r="B477" t="str">
         <v/>
       </c>
     </row>
     <row r="478">
-      <c r="B478" s="1" t="str">
+      <c r="B478" t="str">
         <v/>
       </c>
     </row>
     <row r="479">
-      <c r="B479" s="1" t="str">
+      <c r="B479" t="str">
         <v/>
       </c>
     </row>
     <row r="480">
-      <c r="B480" s="1" t="str">
+      <c r="B480" t="str">
         <v/>
       </c>
     </row>
     <row r="481">
-      <c r="B481" s="1" t="str">
+      <c r="B481" t="str">
         <v/>
       </c>
     </row>
     <row r="482">
-      <c r="B482" s="1" t="str">
+      <c r="B482" t="str">
         <v/>
       </c>
     </row>
     <row r="483">
-      <c r="B483" s="1" t="str">
+      <c r="B483" t="str">
         <v/>
       </c>
     </row>
     <row r="484">
-      <c r="B484" s="1" t="str">
+      <c r="B484" t="str">
         <v/>
       </c>
     </row>
     <row r="485">
-      <c r="B485" s="1" t="str">
+      <c r="B485" t="str">
         <v/>
       </c>
     </row>
     <row r="486">
-      <c r="B486" s="1" t="str">
+      <c r="B486" t="str">
         <v/>
       </c>
     </row>
     <row r="487">
-      <c r="B487" s="1" t="str">
+      <c r="B487" t="str">
         <v/>
       </c>
     </row>
     <row r="488">
-      <c r="B488" s="1" t="str">
+      <c r="B488" t="str">
         <v/>
       </c>
     </row>
     <row r="489">
-      <c r="B489" s="1" t="str">
+      <c r="B489" t="str">
         <v/>
       </c>
     </row>
     <row r="490">
-      <c r="B490" s="1" t="str">
+      <c r="B490" t="str">
         <v/>
       </c>
     </row>
     <row r="491">
-      <c r="B491" s="1" t="str">
+      <c r="B491" t="str">
         <v/>
       </c>
     </row>
     <row r="492">
-      <c r="B492" s="1" t="str">
+      <c r="B492" t="str">
         <v/>
       </c>
     </row>
     <row r="493">
-      <c r="B493" s="1" t="str">
+      <c r="B493" t="str">
         <v/>
       </c>
     </row>
     <row r="494">
-      <c r="B494" s="1" t="str">
+      <c r="B494" t="str">
         <v/>
       </c>
     </row>
     <row r="495">
-      <c r="B495" s="1" t="str">
+      <c r="B495" t="str">
         <v/>
       </c>
     </row>
     <row r="496">
-      <c r="B496" s="1" t="str">
+      <c r="B496" t="str">
         <v/>
       </c>
     </row>
     <row r="497">
-      <c r="B497" s="1" t="str">
+      <c r="B497" t="str">
         <v/>
       </c>
     </row>
     <row r="498">
-      <c r="B498" s="1" t="str">
+      <c r="B498" t="str">
         <v/>
       </c>
     </row>
     <row r="499">
-      <c r="B499" s="1" t="str">
+      <c r="B499" t="str">
         <v/>
       </c>
     </row>
     <row r="500">
-      <c r="B500" s="1" t="str">
+      <c r="B500" t="str">
         <v/>
       </c>
     </row>
     <row r="501">
-      <c r="B501" s="1" t="str">
+      <c r="B501" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E501"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F501"/>
   </ignoredErrors>
 </worksheet>
 </file>